--- a/academic/mendel/data_mendel.xlsx
+++ b/academic/mendel/data_mendel.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_EC39148CE1795F43525B175FCACE999FDE98EFD1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5A248B5-FEF2-4A7A-82D3-E3FED5A9A957}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="2" r:id="rId1"/>
@@ -17,13 +18,27 @@
     <sheet name="P4" sheetId="11" r:id="rId8"/>
     <sheet name="P5" sheetId="12" r:id="rId9"/>
     <sheet name="P6" sheetId="6" r:id="rId10"/>
+    <sheet name="P7" sheetId="13" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="78">
   <si>
     <t>Trait</t>
   </si>
@@ -262,8 +277,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,23 +413,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -422,13 +433,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -466,7 +485,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -500,6 +519,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -534,9 +554,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -709,18 +730,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -733,17 +754,17 @@
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="11" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -768,17 +789,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="6">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="7">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="6">
         <v>27</v>
       </c>
       <c r="E3">
@@ -793,17 +814,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>1</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="7">
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6">
         <v>24</v>
       </c>
       <c r="E4">
@@ -818,17 +839,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="7">
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="6">
         <v>19</v>
       </c>
       <c r="E5">
@@ -843,17 +864,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="6">
         <v>32</v>
       </c>
       <c r="E6">
@@ -868,17 +889,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="7">
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="6">
         <v>26</v>
       </c>
       <c r="E7">
@@ -893,17 +914,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>1</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="6">
         <v>88</v>
       </c>
       <c r="E8">
@@ -918,17 +939,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>1</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="6">
         <v>22</v>
       </c>
       <c r="E9">
@@ -943,17 +964,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>1</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10">
         <v>9</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6">
         <v>28</v>
       </c>
       <c r="E10">
@@ -968,17 +989,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>1</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="C11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="6">
         <v>25</v>
       </c>
       <c r="E11">
@@ -993,17 +1014,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>1</v>
       </c>
-      <c r="B12" s="6">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>12</v>
       </c>
       <c r="E12">
@@ -1018,17 +1039,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>1</v>
       </c>
-      <c r="B13" s="6">
-        <v>2</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>8</v>
       </c>
       <c r="E13">
@@ -1043,17 +1064,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14">
         <v>3</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>7</v>
       </c>
       <c r="E14">
@@ -1068,17 +1089,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>1</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15">
         <v>4</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>16</v>
       </c>
       <c r="E15">
@@ -1093,17 +1114,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>1</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16">
         <v>5</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>11</v>
       </c>
       <c r="E16">
@@ -1118,17 +1139,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>1</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17">
         <v>6</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>6</v>
       </c>
       <c r="E17">
@@ -1143,17 +1164,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>1</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18">
         <v>7</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>24</v>
       </c>
       <c r="E18">
@@ -1168,17 +1189,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>1</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19">
         <v>8</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="6">
         <v>10</v>
       </c>
       <c r="E19">
@@ -1193,17 +1214,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>1</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20">
         <v>9</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="6">
         <v>6</v>
       </c>
       <c r="E20">
@@ -1218,17 +1239,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="8">
-        <v>1</v>
-      </c>
-      <c r="B21" s="9">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="7">
+        <v>1</v>
+      </c>
+      <c r="B21" s="8">
         <v>10</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>7</v>
       </c>
       <c r="E21">
@@ -1243,17 +1264,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>1</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="7">
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="6">
         <v>43</v>
       </c>
       <c r="E22">
@@ -1268,17 +1289,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>1</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="6">
         <v>2</v>
       </c>
       <c r="E23">
@@ -1293,17 +1314,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>1</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="7">
+      <c r="C24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="6">
         <v>14</v>
       </c>
       <c r="E24">
@@ -1318,17 +1339,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>1</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="6">
         <v>15</v>
       </c>
       <c r="E25">
@@ -1343,7 +1364,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>2</v>
       </c>
@@ -1368,17 +1389,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>2</v>
       </c>
-      <c r="B27" s="6">
-        <v>2</v>
-      </c>
-      <c r="C27" s="6" t="s">
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="6">
         <v>32</v>
       </c>
       <c r="E27">
@@ -1393,17 +1414,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>2</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28">
         <v>3</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" t="s">
         <v>4</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="6">
         <v>14</v>
       </c>
       <c r="E28">
@@ -1418,17 +1439,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>2</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29">
         <v>4</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="6">
         <v>70</v>
       </c>
       <c r="E29">
@@ -1443,17 +1464,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>2</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30">
         <v>5</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="6">
         <v>24</v>
       </c>
       <c r="E30">
@@ -1468,17 +1489,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>2</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31">
         <v>6</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" t="s">
         <v>4</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="6">
         <v>20</v>
       </c>
       <c r="E31">
@@ -1493,17 +1514,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>2</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32">
         <v>7</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" t="s">
         <v>4</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="6">
         <v>32</v>
       </c>
       <c r="E32">
@@ -1518,17 +1539,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>2</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33">
         <v>8</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="6">
         <v>44</v>
       </c>
       <c r="E33">
@@ -1543,17 +1564,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>2</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B34">
         <v>9</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="6">
         <v>50</v>
       </c>
       <c r="E34">
@@ -1568,17 +1589,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>2</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35">
         <v>10</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" t="s">
         <v>4</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="6">
         <v>44</v>
       </c>
       <c r="E35">
@@ -1593,17 +1614,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>2</v>
       </c>
-      <c r="B36" s="6">
-        <v>1</v>
-      </c>
-      <c r="C36" s="6" t="s">
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="6">
         <v>11</v>
       </c>
       <c r="E36">
@@ -1618,17 +1639,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>2</v>
       </c>
-      <c r="B37" s="6">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6" t="s">
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
         <v>5</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="6">
         <v>7</v>
       </c>
       <c r="E37">
@@ -1643,17 +1664,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>2</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38">
         <v>3</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" t="s">
         <v>5</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="6">
         <v>5</v>
       </c>
       <c r="E38">
@@ -1668,17 +1689,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>2</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39">
         <v>4</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" t="s">
         <v>5</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="6">
         <v>27</v>
       </c>
       <c r="E39">
@@ -1693,17 +1714,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>2</v>
       </c>
-      <c r="B40" s="6">
+      <c r="B40">
         <v>5</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" t="s">
         <v>5</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="6">
         <v>13</v>
       </c>
       <c r="E40">
@@ -1718,17 +1739,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>2</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B41">
         <v>6</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" t="s">
         <v>5</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="6">
         <v>6</v>
       </c>
       <c r="E41">
@@ -1743,17 +1764,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>2</v>
       </c>
-      <c r="B42" s="6">
+      <c r="B42">
         <v>7</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="6">
         <v>13</v>
       </c>
       <c r="E42">
@@ -1768,17 +1789,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>2</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43">
         <v>8</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" t="s">
         <v>5</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="6">
         <v>9</v>
       </c>
       <c r="E43">
@@ -1793,17 +1814,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>2</v>
       </c>
-      <c r="B44" s="6">
+      <c r="B44">
         <v>9</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" t="s">
         <v>5</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="6">
         <v>14</v>
       </c>
       <c r="E44">
@@ -1818,17 +1839,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="8">
-        <v>2</v>
-      </c>
-      <c r="B45" s="9">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="7">
+        <v>2</v>
+      </c>
+      <c r="B45" s="8">
         <v>10</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D45" s="10">
+      <c r="D45" s="9">
         <v>18</v>
       </c>
       <c r="E45">
@@ -1843,17 +1864,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="11">
-        <v>2</v>
-      </c>
-      <c r="B46" s="12" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="5">
+        <v>2</v>
+      </c>
+      <c r="B46" t="s">
         <v>42</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="13">
+      <c r="D46" s="6">
         <v>32</v>
       </c>
       <c r="E46">
@@ -1868,17 +1889,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="11">
-        <v>2</v>
-      </c>
-      <c r="B47" s="12" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="5">
+        <v>2</v>
+      </c>
+      <c r="B47" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" t="s">
         <v>5</v>
       </c>
-      <c r="D47" s="13">
+      <c r="D47" s="6">
         <v>1</v>
       </c>
       <c r="E47">
@@ -1893,17 +1914,17 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="11">
-        <v>2</v>
-      </c>
-      <c r="B48" s="12" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="5">
+        <v>2</v>
+      </c>
+      <c r="B48" t="s">
         <v>43</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" t="s">
         <v>4</v>
       </c>
-      <c r="D48" s="13">
+      <c r="D48" s="6">
         <v>20</v>
       </c>
       <c r="E48">
@@ -1918,17 +1939,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="11">
-        <v>2</v>
-      </c>
-      <c r="B49" s="12" t="s">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="5">
+        <v>2</v>
+      </c>
+      <c r="B49" t="s">
         <v>43</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" t="s">
         <v>5</v>
       </c>
-      <c r="D49" s="13">
+      <c r="D49" s="6">
         <v>19</v>
       </c>
       <c r="E49">
@@ -1949,11 +1970,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>52</v>
       </c>
@@ -1967,7 +1988,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -1984,7 +2005,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -2001,7 +2022,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -2018,7 +2039,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>55</v>
       </c>
@@ -2035,7 +2056,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -2052,7 +2073,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2069,7 +2090,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -2086,7 +2107,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
@@ -2103,7 +2124,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>4</v>
       </c>
@@ -2120,7 +2141,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -2137,7 +2158,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2154,7 +2175,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>3</v>
       </c>
@@ -2171,7 +2192,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>4</v>
       </c>
@@ -2188,7 +2209,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -2205,7 +2226,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2222,7 +2243,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>3</v>
       </c>
@@ -2239,7 +2260,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>4</v>
       </c>
@@ -2256,7 +2277,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1</v>
       </c>
@@ -2273,7 +2294,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -2290,7 +2311,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2307,7 +2328,388 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F528D33A-0B76-4AB2-B54E-F567FD9F0533}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>4</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>4</v>
       </c>
@@ -2330,14 +2732,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="45.42578125" customWidth="1"/>
+    <col min="4" max="4" width="45.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2360,7 +2762,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2385,7 +2787,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2410,7 +2812,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2435,7 +2837,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -2460,7 +2862,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -2485,7 +2887,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3</v>
       </c>
@@ -2510,7 +2912,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>4</v>
       </c>
@@ -2535,7 +2937,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>4</v>
       </c>
@@ -2560,7 +2962,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>5</v>
       </c>
@@ -2585,7 +2987,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>5</v>
       </c>
@@ -2610,7 +3012,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>6</v>
       </c>
@@ -2635,7 +3037,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>6</v>
       </c>
@@ -2660,7 +3062,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>7</v>
       </c>
@@ -2685,7 +3087,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>7</v>
       </c>
@@ -2716,17 +3118,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2746,7 +3148,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2767,7 +3169,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2788,7 +3190,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2809,7 +3211,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -2830,7 +3232,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -2851,7 +3253,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3</v>
       </c>
@@ -2872,7 +3274,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>4</v>
       </c>
@@ -2893,7 +3295,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>4</v>
       </c>
@@ -2914,7 +3316,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>76</v>
       </c>
@@ -2935,7 +3337,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>76</v>
       </c>
@@ -2956,7 +3358,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>77</v>
       </c>
@@ -2977,7 +3379,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>77</v>
       </c>
@@ -2998,7 +3400,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>6</v>
       </c>
@@ -3019,7 +3421,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>6</v>
       </c>
@@ -3040,7 +3442,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>7</v>
       </c>
@@ -3061,7 +3463,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>7</v>
       </c>
@@ -3088,14 +3490,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -3115,8 +3517,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>73</v>
       </c>
       <c r="B2" t="s">
@@ -3137,8 +3539,8 @@
         <v>0.5625</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="16" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
         <v>73</v>
       </c>
       <c r="B3" t="s">
@@ -3159,8 +3561,8 @@
         <v>0.1875</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
         <v>73</v>
       </c>
       <c r="B4" t="s">
@@ -3181,8 +3583,8 @@
         <v>0.1875</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
         <v>73</v>
       </c>
       <c r="B5" t="s">
@@ -3191,7 +3593,7 @@
       <c r="C5">
         <v>32</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="10">
         <f>SUM(C2:C5)*E5/12</f>
         <v>46.333333333333336</v>
       </c>
@@ -3209,11 +3611,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>47</v>
       </c>
@@ -3221,7 +3623,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -3232,7 +3634,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -3243,7 +3645,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -3260,7 +3662,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3277,7 +3679,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -3294,7 +3696,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3311,7 +3713,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3334,11 +3736,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>47</v>
       </c>
@@ -3346,7 +3748,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -3357,7 +3759,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -3368,7 +3770,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -3385,7 +3787,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3402,7 +3804,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -3419,7 +3821,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3436,7 +3838,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3459,11 +3861,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>47</v>
       </c>
@@ -3471,7 +3873,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -3482,7 +3884,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -3493,7 +3895,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -3510,7 +3912,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3527,7 +3929,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -3544,7 +3946,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3561,7 +3963,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3584,11 +3986,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>47</v>
       </c>
@@ -3596,7 +3998,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -3607,7 +4009,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -3618,7 +4020,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -3635,7 +4037,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3652,7 +4054,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -3669,7 +4071,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3686,7 +4088,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3709,11 +4111,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>48</v>
       </c>
@@ -3721,7 +4123,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -3732,7 +4134,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -3743,7 +4145,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -3760,7 +4162,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3777,7 +4179,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -3794,7 +4196,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3811,7 +4213,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
